--- a/downloads/Manuscript-Consistency-Ledger.xlsx
+++ b/downloads/Manuscript-Consistency-Ledger.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R622f259a8a454fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R7c7c58975df74457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R104581b6732641a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rf1ebc06c7ab14d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R4124debf0fda4c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R3045d686a60843ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -374,7 +374,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Dental Research AI • Free, editable Excel worksheet • Version 2 • 8 September 2026</x:v>
+        <x:v>Dental Research AI • Free editable worksheet • Version 3 • 9 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -411,7 +411,7 @@
         <x:v>1. Read the example</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>Open Completed example. Every study, event, source excerpt, tool record, and action in that sheet is invented for teaching.</x:v>
+        <x:v>Read the Completed example. Published facts are cited to JOP. Proposed plans, practice errors, imagined comments, and AI-use records are labeled teaching exercises; they are not the authors’ original records.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Green = example</x:v>
@@ -472,12 +472,12 @@
         <x:v>Use approved storage</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+    <x:row r="12" ht="150" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Sources / limits</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>Original educational workflow; author responsibility: https://www.icmje.org/recommendations/browse/artificial-intelligence/ai-use-by-authors.html</x:v>
+        <x:v>Ishiguro D, Omar MS, Lin WS, Nagai T. Journal of Prosthodontics. 2026. Early View; supplied PDF pp. 1–9. Effects of scanner type and prosthesis design–luting protocol combinations on the passive fit of interim implant-supported complete-arch fixed dental prostheses https://onlinelibrary.wiley.com/doi/abs/10.1111/jopr.70218 Methods, PDF pp. 2–5; Tables 1–2, PDF pp. 5–6; limitations, PDF p. 7.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Recheck current guidance</x:v>
@@ -499,7 +499,7 @@
         <x:v>Calculation legend</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>Yellow cells are editable inputs; green cells on the example sheet contain invented entries. Dark teal total rows, if present, contain formulas. Do not replace formulas with typed totals.</x:v>
+        <x:v>Yellow cells are editable; green example cells contain published facts and clearly labeled teaching entries. Dark teal timing totals contain formulas. Preserve formulas when editing.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>No color-only status codes</x:v>
@@ -669,7 +669,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R883f69662044444c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25e3857515d9474e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -688,7 +688,7 @@
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Example: manuscript consistency audit</x:v>
+        <x:v>Example: audit deliberately altered laboratory text</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -698,7 +698,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>COMPLETED EXAMPLE • Invented study records and actions; not a real manuscript or peer review.</x:v>
+        <x:v>INVENTED PRACTICE ERRORS, not errors attributed to the authors. Canonical facts come from Ishiguro et al.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -708,7 +708,7 @@
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Canonical teaching facts: 10 manufactured casts; three scans per cast/device; A 70 µm, B 62 µm; surface deviation only; Table 1 is the verified table. Enter your own canonical facts here.</x:v>
+        <x:v>Canonical source: one master cast; 60 prostheses; G3 IOS Direct-to-MUA 10/10 misfits; G6 Lab Direct-to-MUA 0/10; agreement 59/60 = 98.3%. Tables 1–2, PDF pp. 5–6. DOI/link on Guide.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -741,19 +741,19 @@
         <x:v>Major</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Abstract sentence 2</x:v>
+        <x:v>Practice Methods, sentence 1</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
-        <x:v>“Twelve participants” conflicts with the canonical record: 10 manufactured casts.</x:v>
+        <x:v>“Sixty independent casts” conflicts with one master cast and 60 prostheses.</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str">
-        <x:v>“Ten manufactured casts were evaluated.”</x:v>
+        <x:v>Replace with “Sixty prostheses fabricated from one master cast.”</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Lead author — NOT YET DONE</x:v>
+        <x:v>Course reviewer — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="160" customHeight="1">
@@ -761,19 +761,19 @@
         <x:v>Major</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>Results sentence 1; Table 1</x:v>
+        <x:v>Practice Results, sentence 2</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>“70 mm for A and 62 mm for B (Table 2)” conflicts with Table 1, which reports µm.</x:v>
+        <x:v>“Lab Direct-to-MUA had 10/10 misfits; IOS had 0/10” reverses Table 2.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>Change labels to µm and callout to Table 1; preserve 70 and 62.</x:v>
+        <x:v>IOS Direct-to-MUA: 10/10 misfits. Lab Direct-to-MUA: 0/10.</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Corrected</x:v>
+        <x:v>Pending</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Lead author; compared revised text with teaching Table 1, 2026-09-08.</x:v>
+        <x:v>Course reviewer — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="160" customHeight="1">
@@ -781,19 +781,19 @@
         <x:v>Major</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Discussion sentence 3</x:v>
+        <x:v>Practice Results, sentence 3</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>“Improved patient outcomes” exceeds the laboratory surface-deviation outcome.</x:v>
+        <x:v>“Agreement 98.3 mm” uses a length unit for a proportion.</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>“B had lower mean absolute deviation in this laboratory sample.”</x:v>
+        <x:v>Initial agreement 59/60 (98.3%); κ = 0.95.</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Coauthor — NOT YET DONE</x:v>
+        <x:v>Course reviewer — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
@@ -820,7 +820,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd1cf16cce594b1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f18651dbd514b30"/>
   </x:tableParts>
 </x:worksheet>
 </file>